--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:28</t>
+    <t xml:space="preserve">2026-09-10 01:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:43</t>
+    <t xml:space="preserve">2026-09-18 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:39</t>
+    <t xml:space="preserve">2026-09-23 15:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">O Higgins</t>
+    <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
     <t xml:space="preserve">Tortel</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:45</t>
+    <t xml:space="preserve">2026-10-04 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:50</t>
+    <t xml:space="preserve">2026-10-05 16:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
